--- a/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
+++ b/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-1</t>
+    <t>P7-01</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>15:00 05/11/2026</t>
+    <t>15:00 06/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>11:10 11/11/2026</t>
+    <t>11:10 11/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -92,31 +92,18 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Đất san lấp</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">15:00
-05/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00
-06/11/2026</t>
-  </si>
-  <si>
-    <t>Thời gian bắt đầu lấy theo header</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:10
-06/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t/>
@@ -129,11 +116,11 @@
   </si>
   <si>
     <t xml:space="preserve">15:11
-06/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
-06/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -143,11 +130,11 @@
   </si>
   <si>
     <t xml:space="preserve">05:30
-11/11/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">06:30
-11/11/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -157,7 +144,7 @@
   </si>
   <si>
     <t xml:space="preserve">07:12
-11/11/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -167,11 +154,11 @@
   </si>
   <si>
     <t xml:space="preserve">07:13
-11/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:54
-11/11/2026</t>
+11/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:55
+11/03/2026</t>
   </si>
   <si>
     <t>15</t>
@@ -180,12 +167,8 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">08:55
-11/11/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">09:27
-11/11/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>16</t>
@@ -195,38 +178,32 @@
   </si>
   <si>
     <t xml:space="preserve">09:30
-11/11/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:05
-11/11/2026</t>
+11/03/2026</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:18
-11/11/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
-11/11/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:10
-11/11/2026</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Cuội đá màu sắc TT rất chặt</t>
-  </si>
-  <si>
-    <t>Lớp địa chất tại đáy hố khoan</t>
+11/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -263,7 +240,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -339,11 +316,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -356,7 +328,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,12 +367,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -431,11 +403,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -531,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -566,17 +533,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,22 +599,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -673,7 +631,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -1033,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1233,19 +1191,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.68</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="H11" s="5">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>5.16</v>
+        <v>39</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1262,63 +1220,63 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="G12" s="9">
-        <v>-7.6</v>
+        <v>-9</v>
       </c>
       <c r="H12" s="9">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="I12" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="J12" s="8">
-        <v>39</v>
+        <v>1.4</v>
+      </c>
+      <c r="J12" s="12">
+        <v>4.42</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="12">
-        <v>-7.6</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="F13" s="13">
         <v>-9</v>
       </c>
-      <c r="H13" s="12">
-        <v>0.32</v>
-      </c>
-      <c r="I13" s="12">
-        <v>1.4</v>
-      </c>
-      <c r="J13" s="15">
-        <v>4.42</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>34</v>
+      <c r="G13" s="13">
+        <v>-18</v>
+      </c>
+      <c r="H13" s="13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="13">
+        <v>9</v>
+      </c>
+      <c r="J13" s="8">
+        <v>9</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1332,63 +1290,63 @@
         <v>40</v>
       </c>
       <c r="D14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>42</v>
-      </c>
       <c r="F14" s="16">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="G14" s="16">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="H14" s="16">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I14" s="16">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="J14" s="8">
-        <v>9</v>
+        <v>5.86</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="19">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="G15" s="19">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="H15" s="19">
         <v>0.7</v>
       </c>
       <c r="I15" s="19">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J15" s="8">
-        <v>6.29</v>
+        <v>5.71</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1402,220 +1360,152 @@
         <v>47</v>
       </c>
       <c r="D16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>49</v>
-      </c>
       <c r="F16" s="22">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="G16" s="22">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="H16" s="22">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="I16" s="22">
-        <v>3.7</v>
-      </c>
-      <c r="J16" s="15">
-        <v>2.2</v>
+        <v>10</v>
+      </c>
+      <c r="J16" s="8">
+        <v>6.52</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>53</v>
-      </c>
       <c r="F17" s="25">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="G17" s="25">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="H17" s="25">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="I17" s="25">
-        <v>10</v>
-      </c>
-      <c r="J17" s="8">
-        <v>18.75</v>
+        <v>2.5</v>
+      </c>
+      <c r="J17" s="12">
+        <v>4.29</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>57</v>
-      </c>
       <c r="F18" s="28">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="G18" s="28">
-        <v>-38.6</v>
+        <v>-40</v>
       </c>
       <c r="H18" s="28">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="I18" s="28">
-        <v>2.5</v>
-      </c>
-      <c r="J18" s="15">
-        <v>4.29</v>
+        <v>1.4</v>
+      </c>
+      <c r="J18" s="8">
+        <v>6.46</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="31">
+        <v>-40</v>
+      </c>
+      <c r="G19" s="31">
+        <v>-45.1</v>
+      </c>
+      <c r="H19" s="31">
+        <v>0.83</v>
+      </c>
+      <c r="I19" s="31">
+        <v>5.1</v>
+      </c>
+      <c r="J19" s="8">
+        <v>6.12</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="31">
-        <v>-38.6</v>
-      </c>
-      <c r="G19" s="31">
-        <v>-40</v>
-      </c>
-      <c r="H19" s="31">
-        <v>0.22</v>
-      </c>
-      <c r="I19" s="31">
-        <v>1.4</v>
-      </c>
-      <c r="J19" s="8">
-        <v>6.46</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="34">
-        <v>-40</v>
-      </c>
-      <c r="G20" s="34">
-        <v>-45.1</v>
-      </c>
-      <c r="H20" s="34">
-        <v>0.83</v>
-      </c>
-      <c r="I20" s="34">
-        <v>5.1</v>
-      </c>
-      <c r="J20" s="8">
-        <v>6.12</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="G21" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="H21" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="I21" s="16">
-        <v>0</v>
-      </c>
-      <c r="J21" s="15">
-        <v>0</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-    </row>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1674,8 +1564,6 @@
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1686,7 +1574,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1696,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1709,31 +1597,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1750,19 +1638,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.68</v>
+        <v>-1.1</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="G2" s="5">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>5.16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1779,48 +1667,48 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="F3" s="9">
-        <v>-7.6</v>
+        <v>-9</v>
       </c>
       <c r="G3" s="9">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="H3" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="I3" s="8">
-        <v>39</v>
+        <v>1.4</v>
+      </c>
+      <c r="I3" s="12">
+        <v>4.42</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
-        <v>-7.6</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="E4" s="13">
         <v>-9</v>
       </c>
-      <c r="G4" s="12">
-        <v>0.32</v>
-      </c>
-      <c r="H4" s="12">
-        <v>1.4</v>
-      </c>
-      <c r="I4" s="15">
-        <v>4.42</v>
+      <c r="F4" s="13">
+        <v>-18</v>
+      </c>
+      <c r="G4" s="13">
+        <v>1</v>
+      </c>
+      <c r="H4" s="13">
+        <v>9</v>
+      </c>
+      <c r="I4" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1837,19 +1725,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="F5" s="16">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="G5" s="16">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H5" s="16">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="I5" s="8">
-        <v>9</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1860,25 +1748,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="F6" s="19">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="G6" s="19">
         <v>0.7</v>
       </c>
       <c r="H6" s="19">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I6" s="8">
-        <v>6.29</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1895,19 +1783,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="F7" s="22">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="G7" s="22">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="H7" s="22">
-        <v>3.7</v>
-      </c>
-      <c r="I7" s="15">
-        <v>2.2</v>
+        <v>10</v>
+      </c>
+      <c r="I7" s="8">
+        <v>6.52</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1918,25 +1806,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="F8" s="25">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="G8" s="25">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="25">
-        <v>10</v>
-      </c>
-      <c r="I8" s="8">
-        <v>18.75</v>
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="12">
+        <v>4.29</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1947,25 +1835,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="F9" s="28">
-        <v>-38.6</v>
+        <v>-40</v>
       </c>
       <c r="G9" s="28">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="H9" s="28">
-        <v>2.5</v>
-      </c>
-      <c r="I9" s="15">
-        <v>4.29</v>
+        <v>1.4</v>
+      </c>
+      <c r="I9" s="8">
+        <v>6.46</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1976,112 +1864,54 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-38.6</v>
+        <v>-40</v>
       </c>
       <c r="F10" s="31">
-        <v>-40</v>
+        <v>-45.1</v>
       </c>
       <c r="G10" s="31">
-        <v>0.22</v>
+        <v>0.83</v>
       </c>
       <c r="H10" s="31">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="I10" s="8">
-        <v>6.46</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-40</v>
-      </c>
-      <c r="F11" s="34">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="36">
+        <v>9</v>
+      </c>
+      <c r="E11" s="36">
+        <v>-1.1</v>
+      </c>
+      <c r="F11" s="36">
         <v>-45.1</v>
       </c>
-      <c r="G11" s="34">
-        <v>0.83</v>
-      </c>
-      <c r="H11" s="34">
-        <v>5.1</v>
-      </c>
-      <c r="I11" s="8">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="16">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="F12" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="G12" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="16">
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="39">
-        <v>11</v>
-      </c>
-      <c r="E13" s="39">
-        <v>-3.68</v>
-      </c>
-      <c r="F13" s="39">
-        <v>-45.1</v>
-      </c>
-      <c r="G13" s="39">
-        <v>7.03</v>
-      </c>
-      <c r="H13" s="39">
-        <v>46.58</v>
-      </c>
-      <c r="I13" s="39">
-        <v>6.62</v>
+      <c r="G11" s="36">
+        <v>6.05</v>
+      </c>
+      <c r="H11" s="36">
+        <v>44</v>
+      </c>
+      <c r="I11" s="36">
+        <v>7.27</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
+++ b/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-01</t>
+    <t>P7-1</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>15:00 06/03/2026</t>
+    <t>15:00 05/11/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>11:10 11/03/2026</t>
+    <t>11:10 11/11/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -92,18 +92,31 @@
     <t>Ghi chú</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Đất san lấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00
+05/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00
+06/11/2026</t>
+  </si>
+  <si>
+    <t>Thời gian bắt đầu lấy theo header</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">15:00
-06/03/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">15:10
-06/03/2026</t>
+06/11/2026</t>
   </si>
   <si>
     <t/>
@@ -116,11 +129,11 @@
   </si>
   <si>
     <t xml:space="preserve">15:11
-06/03/2026</t>
+06/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
-06/03/2026</t>
+06/11/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -130,11 +143,11 @@
   </si>
   <si>
     <t xml:space="preserve">05:30
-11/03/2026</t>
+11/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">06:30
-11/03/2026</t>
+11/11/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -144,7 +157,7 @@
   </si>
   <si>
     <t xml:space="preserve">07:12
-11/03/2026</t>
+11/11/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -154,21 +167,25 @@
   </si>
   <si>
     <t xml:space="preserve">07:13
-11/03/2026</t>
+11/11/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:54
+11/11/2026</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">07:55
-11/03/2026</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+11/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">09:27
-11/03/2026</t>
+11/11/2026</t>
   </si>
   <si>
     <t>16</t>
@@ -178,32 +195,38 @@
   </si>
   <si>
     <t xml:space="preserve">09:30
-11/03/2026</t>
+11/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:05
-11/03/2026</t>
-  </si>
-  <si>
-    <t>8</t>
+11/11/2026</t>
   </si>
   <si>
     <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:18
-11/03/2026</t>
+11/11/2026</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
-11/03/2026</t>
+11/11/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:10
-11/03/2026</t>
+11/11/2026</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Cuội đá màu sắc TT rất chặt</t>
+  </si>
+  <si>
+    <t>Lớp địa chất tại đáy hố khoan</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -240,7 +263,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -316,6 +339,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF134E4A"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -328,7 +356,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,12 +395,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -403,6 +431,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -533,17 +566,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -599,13 +632,22 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -631,7 +673,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -991,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1191,19 +1233,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
+        <v>-3.68</v>
+      </c>
+      <c r="G11" s="5">
         <v>-1.1</v>
       </c>
-      <c r="G11" s="5">
-        <v>-7.6</v>
-      </c>
       <c r="H11" s="5">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>6.5</v>
+        <v>2.58</v>
       </c>
       <c r="J11" s="8">
-        <v>39</v>
+        <v>5.16</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1220,63 +1262,63 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="9">
+        <v>-1.1</v>
+      </c>
+      <c r="G12" s="9">
+        <v>-7.6</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="I12" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="J12" s="8">
+        <v>39</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="9">
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="12">
         <v>-7.6</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G13" s="12">
         <v>-9</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H13" s="12">
         <v>0.32</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I13" s="12">
         <v>1.4</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J13" s="15">
         <v>4.42</v>
       </c>
-      <c r="K12" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="13">
-        <v>-9</v>
-      </c>
-      <c r="G13" s="13">
-        <v>-18</v>
-      </c>
-      <c r="H13" s="13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="13">
-        <v>9</v>
-      </c>
-      <c r="J13" s="8">
-        <v>9</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>30</v>
+      <c r="K13" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1290,63 +1332,63 @@
         <v>40</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="16">
+        <v>-9</v>
+      </c>
+      <c r="G14" s="16">
         <v>-18</v>
       </c>
-      <c r="G14" s="16">
-        <v>-22.1</v>
-      </c>
       <c r="H14" s="16">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I14" s="16">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="J14" s="8">
-        <v>5.86</v>
+        <v>9</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>44</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="19">
-        <v>-22.1</v>
+        <v>-18</v>
       </c>
       <c r="G15" s="19">
-        <v>-26.1</v>
+        <v>-22.4</v>
       </c>
       <c r="H15" s="19">
         <v>0.7</v>
       </c>
       <c r="I15" s="19">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J15" s="8">
-        <v>5.71</v>
+        <v>6.29</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,152 +1402,220 @@
         <v>47</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="22">
+        <v>-22.4</v>
+      </c>
+      <c r="G16" s="22">
         <v>-26.1</v>
       </c>
-      <c r="G16" s="22">
-        <v>-36.1</v>
-      </c>
       <c r="H16" s="22">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="I16" s="22">
-        <v>10</v>
-      </c>
-      <c r="J16" s="8">
-        <v>6.52</v>
+        <v>3.7</v>
+      </c>
+      <c r="J16" s="15">
+        <v>2.2</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" s="25">
+        <v>-26.1</v>
+      </c>
+      <c r="G17" s="25">
         <v>-36.1</v>
       </c>
-      <c r="G17" s="25">
-        <v>-38.6</v>
-      </c>
       <c r="H17" s="25">
-        <v>0.58</v>
+        <v>1.53</v>
       </c>
       <c r="I17" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="J17" s="12">
-        <v>4.29</v>
+        <v>10</v>
+      </c>
+      <c r="J17" s="8">
+        <v>6.52</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F18" s="28">
+        <v>-36.1</v>
+      </c>
+      <c r="G18" s="28">
         <v>-38.6</v>
       </c>
-      <c r="G18" s="28">
-        <v>-40</v>
-      </c>
       <c r="H18" s="28">
-        <v>0.22</v>
+        <v>0.58</v>
       </c>
       <c r="I18" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="J18" s="8">
-        <v>6.46</v>
+        <v>2.5</v>
+      </c>
+      <c r="J18" s="15">
+        <v>4.29</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F19" s="31">
+        <v>-38.6</v>
+      </c>
+      <c r="G19" s="31">
         <v>-40</v>
       </c>
-      <c r="G19" s="31">
+      <c r="H19" s="31">
+        <v>0.22</v>
+      </c>
+      <c r="I19" s="31">
+        <v>1.4</v>
+      </c>
+      <c r="J19" s="8">
+        <v>6.46</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="34">
+        <v>-40</v>
+      </c>
+      <c r="G20" s="34">
         <v>-45.1</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H20" s="34">
         <v>0.83</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I20" s="34">
         <v>5.1</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J20" s="8">
         <v>6.12</v>
       </c>
-      <c r="K19" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="K20" s="35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="16">
+        <v>-45.1</v>
+      </c>
+      <c r="G21" s="16">
+        <v>-45.1</v>
+      </c>
+      <c r="H21" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="16">
+        <v>0</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+    </row>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1564,6 +1674,8 @@
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1574,7 +1686,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A24:K24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1584,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1597,31 +1709,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1638,19 +1750,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
+        <v>-3.68</v>
+      </c>
+      <c r="F2" s="5">
         <v>-1.1</v>
       </c>
-      <c r="F2" s="5">
-        <v>-7.6</v>
-      </c>
       <c r="G2" s="5">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>6.5</v>
+        <v>2.58</v>
       </c>
       <c r="I2" s="8">
-        <v>39</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1667,48 +1779,48 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
+        <v>-1.1</v>
+      </c>
+      <c r="F3" s="9">
         <v>-7.6</v>
       </c>
-      <c r="F3" s="9">
+      <c r="G3" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="H3" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="I3" s="8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12">
+        <v>-7.6</v>
+      </c>
+      <c r="F4" s="12">
         <v>-9</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G4" s="12">
         <v>0.32</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H4" s="12">
         <v>1.4</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I4" s="15">
         <v>4.42</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="13">
-        <v>1</v>
-      </c>
-      <c r="E4" s="13">
-        <v>-9</v>
-      </c>
-      <c r="F4" s="13">
-        <v>-18</v>
-      </c>
-      <c r="G4" s="13">
-        <v>1</v>
-      </c>
-      <c r="H4" s="13">
-        <v>9</v>
-      </c>
-      <c r="I4" s="8">
-        <v>9</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1725,19 +1837,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
+        <v>-9</v>
+      </c>
+      <c r="F5" s="16">
         <v>-18</v>
       </c>
-      <c r="F5" s="16">
-        <v>-22.1</v>
-      </c>
       <c r="G5" s="16">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H5" s="16">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="I5" s="8">
-        <v>5.86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1748,25 +1860,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-22.1</v>
+        <v>-18</v>
       </c>
       <c r="F6" s="19">
-        <v>-26.1</v>
+        <v>-22.4</v>
       </c>
       <c r="G6" s="19">
         <v>0.7</v>
       </c>
       <c r="H6" s="19">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I6" s="8">
-        <v>5.71</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1783,19 +1895,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
+        <v>-22.4</v>
+      </c>
+      <c r="F7" s="22">
         <v>-26.1</v>
       </c>
-      <c r="F7" s="22">
-        <v>-36.1</v>
-      </c>
       <c r="G7" s="22">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="H7" s="22">
-        <v>10</v>
-      </c>
-      <c r="I7" s="8">
-        <v>6.52</v>
+        <v>3.7</v>
+      </c>
+      <c r="I7" s="15">
+        <v>2.2</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1806,25 +1918,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
+        <v>-26.1</v>
+      </c>
+      <c r="F8" s="25">
         <v>-36.1</v>
       </c>
-      <c r="F8" s="25">
-        <v>-38.6</v>
-      </c>
       <c r="G8" s="25">
-        <v>0.58</v>
+        <v>1.53</v>
       </c>
       <c r="H8" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="I8" s="12">
-        <v>4.29</v>
+        <v>10</v>
+      </c>
+      <c r="I8" s="8">
+        <v>6.52</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1835,25 +1947,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
+        <v>-36.1</v>
+      </c>
+      <c r="F9" s="28">
         <v>-38.6</v>
       </c>
-      <c r="F9" s="28">
-        <v>-40</v>
-      </c>
       <c r="G9" s="28">
-        <v>0.22</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="I9" s="8">
-        <v>6.46</v>
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="15">
+        <v>4.29</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1864,54 +1976,112 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
+        <v>-38.6</v>
+      </c>
+      <c r="F10" s="31">
         <v>-40</v>
       </c>
-      <c r="F10" s="31">
+      <c r="G10" s="31">
+        <v>0.22</v>
+      </c>
+      <c r="H10" s="31">
+        <v>1.4</v>
+      </c>
+      <c r="I10" s="8">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="34">
+        <v>1</v>
+      </c>
+      <c r="E11" s="34">
+        <v>-40</v>
+      </c>
+      <c r="F11" s="34">
         <v>-45.1</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G11" s="34">
         <v>0.83</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H11" s="34">
         <v>5.1</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I11" s="8">
         <v>6.12</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="36">
-        <v>9</v>
-      </c>
-      <c r="E11" s="36">
-        <v>-1.1</v>
-      </c>
-      <c r="F11" s="36">
+    <row r="12" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="16">
+        <v>1</v>
+      </c>
+      <c r="E12" s="16">
         <v>-45.1</v>
       </c>
-      <c r="G11" s="36">
-        <v>6.05</v>
-      </c>
-      <c r="H11" s="36">
-        <v>44</v>
-      </c>
-      <c r="I11" s="36">
-        <v>7.27</v>
+      <c r="F12" s="16">
+        <v>-45.1</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="39">
+        <v>11</v>
+      </c>
+      <c r="E13" s="39">
+        <v>-3.68</v>
+      </c>
+      <c r="F13" s="39">
+        <v>-45.1</v>
+      </c>
+      <c r="G13" s="39">
+        <v>8.03</v>
+      </c>
+      <c r="H13" s="39">
+        <v>46.58</v>
+      </c>
+      <c r="I13" s="39">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
+++ b/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-1</t>
+    <t>P7-01</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>15:00 05/11/2026</t>
+    <t>15:00 06/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>11:10 11/11/2026</t>
+    <t>11:10 11/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -92,31 +92,18 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Đất san lấp</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">15:00
-05/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00
-06/11/2026</t>
-  </si>
-  <si>
-    <t>Thời gian bắt đầu lấy theo header</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:10
-06/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t/>
@@ -129,11 +116,11 @@
   </si>
   <si>
     <t xml:space="preserve">15:11
-06/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
-06/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -143,11 +130,11 @@
   </si>
   <si>
     <t xml:space="preserve">05:30
-11/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">06:30
-11/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -157,7 +144,7 @@
   </si>
   <si>
     <t xml:space="preserve">07:12
-11/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -167,11 +154,11 @@
   </si>
   <si>
     <t xml:space="preserve">07:13
-11/11/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:54
-11/11/2026</t>
+06/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:55
+06/03/2026</t>
   </si>
   <si>
     <t>15</t>
@@ -180,12 +167,8 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">07:55
-11/11/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">09:27
-11/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>16</t>
@@ -195,38 +178,32 @@
   </si>
   <si>
     <t xml:space="preserve">09:30
-11/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:05
-11/11/2026</t>
-  </si>
-  <si>
-    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+06/03/2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:18
-11/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
-11/11/2026</t>
+06/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:10
-11/11/2026</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Cuội đá màu sắc TT rất chặt</t>
-  </si>
-  <si>
-    <t>Lớp địa chất tại đáy hố khoan</t>
+06/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -263,7 +240,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -339,11 +316,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -356,7 +328,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,12 +367,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -431,11 +403,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -531,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -566,17 +533,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,22 +599,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -673,7 +631,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -1033,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1233,19 +1191,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.68</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="H11" s="5">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>5.16</v>
+        <v>39</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1262,63 +1220,63 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="G12" s="9">
-        <v>-7.6</v>
+        <v>-9</v>
       </c>
       <c r="H12" s="9">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="I12" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="J12" s="8">
-        <v>39</v>
+        <v>1.4</v>
+      </c>
+      <c r="J12" s="12">
+        <v>4.42</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="12">
-        <v>-7.6</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="F13" s="13">
         <v>-9</v>
       </c>
-      <c r="H13" s="12">
-        <v>0.32</v>
-      </c>
-      <c r="I13" s="12">
-        <v>1.4</v>
-      </c>
-      <c r="J13" s="15">
-        <v>4.42</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>34</v>
+      <c r="G13" s="13">
+        <v>-18</v>
+      </c>
+      <c r="H13" s="13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="13">
+        <v>9</v>
+      </c>
+      <c r="J13" s="8">
+        <v>9</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1332,63 +1290,63 @@
         <v>40</v>
       </c>
       <c r="D14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>42</v>
-      </c>
       <c r="F14" s="16">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="G14" s="16">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="H14" s="16">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I14" s="16">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="J14" s="8">
-        <v>9</v>
+        <v>5.86</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="19">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="G15" s="19">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="H15" s="19">
         <v>0.7</v>
       </c>
       <c r="I15" s="19">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J15" s="8">
-        <v>6.29</v>
+        <v>5.71</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1402,220 +1360,152 @@
         <v>47</v>
       </c>
       <c r="D16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>49</v>
-      </c>
       <c r="F16" s="22">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="G16" s="22">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="H16" s="22">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="I16" s="22">
-        <v>3.7</v>
-      </c>
-      <c r="J16" s="15">
-        <v>2.2</v>
+        <v>10</v>
+      </c>
+      <c r="J16" s="8">
+        <v>6.52</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>53</v>
-      </c>
       <c r="F17" s="25">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="G17" s="25">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="H17" s="25">
-        <v>1.53</v>
+        <v>0.58</v>
       </c>
       <c r="I17" s="25">
-        <v>10</v>
-      </c>
-      <c r="J17" s="8">
-        <v>6.52</v>
+        <v>2.5</v>
+      </c>
+      <c r="J17" s="12">
+        <v>4.29</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>57</v>
-      </c>
       <c r="F18" s="28">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="G18" s="28">
-        <v>-38.6</v>
+        <v>-40</v>
       </c>
       <c r="H18" s="28">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="I18" s="28">
-        <v>2.5</v>
-      </c>
-      <c r="J18" s="15">
-        <v>4.29</v>
+        <v>1.4</v>
+      </c>
+      <c r="J18" s="8">
+        <v>6.46</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="31">
+        <v>-40</v>
+      </c>
+      <c r="G19" s="31">
+        <v>-45.1</v>
+      </c>
+      <c r="H19" s="31">
+        <v>0.83</v>
+      </c>
+      <c r="I19" s="31">
+        <v>5.1</v>
+      </c>
+      <c r="J19" s="8">
+        <v>6.12</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="31">
-        <v>-38.6</v>
-      </c>
-      <c r="G19" s="31">
-        <v>-40</v>
-      </c>
-      <c r="H19" s="31">
-        <v>0.22</v>
-      </c>
-      <c r="I19" s="31">
-        <v>1.4</v>
-      </c>
-      <c r="J19" s="8">
-        <v>6.46</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="34">
-        <v>-40</v>
-      </c>
-      <c r="G20" s="34">
-        <v>-45.1</v>
-      </c>
-      <c r="H20" s="34">
-        <v>0.83</v>
-      </c>
-      <c r="I20" s="34">
-        <v>5.1</v>
-      </c>
-      <c r="J20" s="8">
-        <v>6.12</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="G21" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="H21" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="I21" s="16">
-        <v>0</v>
-      </c>
-      <c r="J21" s="15">
-        <v>0</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-    </row>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1674,8 +1564,6 @@
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1686,7 +1574,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1696,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1709,31 +1597,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1750,19 +1638,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.68</v>
+        <v>-1.1</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="G2" s="5">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>5.16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1779,48 +1667,48 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.1</v>
+        <v>-7.6</v>
       </c>
       <c r="F3" s="9">
-        <v>-7.6</v>
+        <v>-9</v>
       </c>
       <c r="G3" s="9">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="H3" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="I3" s="8">
-        <v>39</v>
+        <v>1.4</v>
+      </c>
+      <c r="I3" s="12">
+        <v>4.42</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
-        <v>-7.6</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="E4" s="13">
         <v>-9</v>
       </c>
-      <c r="G4" s="12">
-        <v>0.32</v>
-      </c>
-      <c r="H4" s="12">
-        <v>1.4</v>
-      </c>
-      <c r="I4" s="15">
-        <v>4.42</v>
+      <c r="F4" s="13">
+        <v>-18</v>
+      </c>
+      <c r="G4" s="13">
+        <v>1</v>
+      </c>
+      <c r="H4" s="13">
+        <v>9</v>
+      </c>
+      <c r="I4" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1837,19 +1725,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="F5" s="16">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="G5" s="16">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H5" s="16">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="I5" s="8">
-        <v>9</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1860,25 +1748,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-18</v>
+        <v>-22.1</v>
       </c>
       <c r="F6" s="19">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="G6" s="19">
         <v>0.7</v>
       </c>
       <c r="H6" s="19">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I6" s="8">
-        <v>6.29</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1895,19 +1783,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-22.4</v>
+        <v>-26.1</v>
       </c>
       <c r="F7" s="22">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="G7" s="22">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="H7" s="22">
-        <v>3.7</v>
-      </c>
-      <c r="I7" s="15">
-        <v>2.2</v>
+        <v>10</v>
+      </c>
+      <c r="I7" s="8">
+        <v>6.52</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1918,25 +1806,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-26.1</v>
+        <v>-36.1</v>
       </c>
       <c r="F8" s="25">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="G8" s="25">
-        <v>1.53</v>
+        <v>0.58</v>
       </c>
       <c r="H8" s="25">
-        <v>10</v>
-      </c>
-      <c r="I8" s="8">
-        <v>6.52</v>
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="12">
+        <v>4.29</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1947,25 +1835,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-36.1</v>
+        <v>-38.6</v>
       </c>
       <c r="F9" s="28">
-        <v>-38.6</v>
+        <v>-40</v>
       </c>
       <c r="G9" s="28">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="H9" s="28">
-        <v>2.5</v>
-      </c>
-      <c r="I9" s="15">
-        <v>4.29</v>
+        <v>1.4</v>
+      </c>
+      <c r="I9" s="8">
+        <v>6.46</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1976,112 +1864,54 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-38.6</v>
+        <v>-40</v>
       </c>
       <c r="F10" s="31">
-        <v>-40</v>
+        <v>-45.1</v>
       </c>
       <c r="G10" s="31">
-        <v>0.22</v>
+        <v>0.83</v>
       </c>
       <c r="H10" s="31">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="I10" s="8">
-        <v>6.46</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-40</v>
-      </c>
-      <c r="F11" s="34">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="36">
+        <v>9</v>
+      </c>
+      <c r="E11" s="36">
+        <v>-1.1</v>
+      </c>
+      <c r="F11" s="36">
         <v>-45.1</v>
       </c>
-      <c r="G11" s="34">
-        <v>0.83</v>
-      </c>
-      <c r="H11" s="34">
-        <v>5.1</v>
-      </c>
-      <c r="I11" s="8">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="16">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="F12" s="16">
-        <v>-45.1</v>
-      </c>
-      <c r="G12" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="16">
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="39">
-        <v>11</v>
-      </c>
-      <c r="E13" s="39">
-        <v>-3.68</v>
-      </c>
-      <c r="F13" s="39">
-        <v>-45.1</v>
-      </c>
-      <c r="G13" s="39">
-        <v>8.03</v>
-      </c>
-      <c r="H13" s="39">
-        <v>46.58</v>
-      </c>
-      <c r="I13" s="39">
-        <v>5.8</v>
+      <c r="G11" s="36">
+        <v>6.05</v>
+      </c>
+      <c r="H11" s="36">
+        <v>44</v>
+      </c>
+      <c r="I11" s="36">
+        <v>7.27</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
+++ b/SGC-CKN/Excel/bfbb6fcb-3e28-4e33-8c52-fcea3701ed8b_Lô_CT-02_P7-1_D800_11-11-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
   <si>
     <t>Dự án</t>
   </si>
@@ -130,11 +130,11 @@
   </si>
   <si>
     <t xml:space="preserve">05:30
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">06:30
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -144,7 +144,7 @@
   </si>
   <si>
     <t xml:space="preserve">07:12
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -154,11 +154,11 @@
   </si>
   <si>
     <t xml:space="preserve">07:13
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:55
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>15</t>
@@ -168,21 +168,21 @@
   </si>
   <si>
     <t xml:space="preserve">09:27
-06/03/2026</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+11/03/2026</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">09:30
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:05
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -192,18 +192,15 @@
   </si>
   <si>
     <t xml:space="preserve">10:18
-06/03/2026</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:10
-06/03/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1456,19 +1453,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>57</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>58</v>
       </c>
       <c r="F19" s="31">
         <v>-40</v>
@@ -1491,7 +1488,7 @@
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -1597,31 +1594,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1864,7 +1861,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1887,7 +1884,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="36" t="s">
         <v>30</v>
